--- a/WorkBot/main/data/order_archive/BJ's/BJ's_Triphammer_20260515.xlsx
+++ b/WorkBot/main/data/order_archive/BJ's/BJ's_Triphammer_20260515.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,27 +494,6 @@
       </c>
       <c r="E6" t="n">
         <v>11.99</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2338427022</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Whitefish Salad (Bulk)</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>10</v>
-      </c>
-      <c r="D7" t="n">
-        <v>17.99</v>
-      </c>
-      <c r="E7" t="n">
-        <v>179.9</v>
       </c>
     </row>
   </sheetData>
